--- a/backend/data/financials_by_company/1488.HK.xlsx
+++ b/backend/data/financials_by_company/1488.HK.xlsx
@@ -4569,7 +4569,7 @@
         <v>-5246000</v>
       </c>
       <c r="BN2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BO2" t="n">
         <v>4.462</v>
@@ -4818,7 +4818,7 @@
         <v>0</v>
       </c>
       <c r="EE2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EF2" t="n">
         <v>-16.666664</v>
